--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-URT-FRM-09_saha_turu_ve_vardiya_amirinin_gunluk_kontrol_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-URT-FRM-09_saha_turu_ve_vardiya_amirinin_gunluk_kontrol_listesi.xlsx
@@ -932,7 +932,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Saha Turu ve Vardiya Amirinin Günlük Kontrol Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6d7add2a3f4b7c"/>
   <x:tableParts count="1">
@@ -1235,7 +1236,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Saha Turu ve Vardiya Amirinin Günlük Kontrol Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c1032a223cb45e6"/>
   <x:tableParts count="1">
